--- a/aq_files/0741.xlsx
+++ b/aq_files/0741.xlsx
@@ -2,12 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operators" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,10 +16,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -34,7 +41,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,15 +49,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,28 +438,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Details / Options</t>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Details</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -446,17 +471,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arithmetic operator example:</t>
+          <t>Which keyword is used to define a function?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A) + B) &amp;&amp; C) = D) None</t>
+          <t>A) func B) def C) function D) define</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -468,17 +493,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Comparison operator:</t>
+          <t>Functions help in:</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A) == B) + C) / D) None</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) Code reuse B) UI C) Styling D) None</t>
         </is>
       </c>
     </row>
@@ -490,83 +510,78 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Logical operator:</t>
+          <t>What does return do?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A) and B) + C) = D) None</t>
+          <t>A) Outputs value B) Prints C) Stops loop D) None</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Write program to check greater number using operators.</t>
+          <t>Default return value if no return?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>A) 0 B) None C) Empty D) Error</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Write program to check even using % operator.</t>
+          <t>Function name should be:</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>A) descriptive B) random C) number D) None</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Assignment operator:</t>
+          <t>Write a function to check if a number is prime.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A) = B) == C) != D) None</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -578,17 +593,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Write program using logical operators.</t>
+          <t>Write a function to return factorial of a number.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -600,17 +615,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Write program to find max using ternary operator.</t>
+          <t>Write a function to check palindrome string.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -622,61 +637,61 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Write program to calculate simple interest.</t>
+          <t>Write a function to return sum of digits.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bitwise operator example:</t>
+          <t>Write a function to find max of 3 numbers.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A) &amp; B) + C) = D) None</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Identity operator:</t>
+          <t>Write a function to reverse a list.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A) is B) == C) != D) None</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -688,17 +703,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Write program to swap numbers using operators.</t>
+          <t>Write a function to count vowels in string.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -710,39 +725,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Write program using compound operators.</t>
+          <t>Write a function to check Armstrong number.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Operator precedence defines:</t>
+          <t>Write a function to return Fibonacci series.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A) Order B) Type C) Value D) None</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -754,17 +769,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Write program to evaluate expression.</t>
+          <t>Write a function to remove duplicates from list.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -776,17 +791,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Write program using bitwise AND.</t>
+          <t>Write a function to sort list without built-in.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -798,39 +813,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Write program using logical conditions.</t>
+          <t>Write a function to find second largest element.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Not operator:</t>
+          <t>Write a function to count frequency of elements.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>A) not B) ! C) ~ D) None</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
@@ -842,65 +857,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Write program using multiple operators.</t>
+          <t>Write a function to check if list is sorted.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Write code and execute</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>Coding</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Division operator:</t>
+          <t>Write a function to merge two lists.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>A) / B) * C) - D) None</t>
+          <t>LeetCode-style / logic-based</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Easy</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Coding</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Write program to check divisibility.</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Write code and execute</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Easy</t>
+          <t>Coding</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>